--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1895-new.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1895-new.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A8D58E-A69D-41F0-8207-E7E00B1C8725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{645A4775-945C-4CA3-BBD1-0F47EC833CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -972,7 +972,7 @@
       <name val="Arial Unicode MS"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1032,6 +1032,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1045,7 +1051,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1196,6 +1202,9 @@
     </xf>
     <xf numFmtId="3" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6378,8 +6387,8 @@
       <c r="K75" s="8">
         <v>101703</v>
       </c>
-      <c r="L75" s="8">
-        <v>80907</v>
+      <c r="L75" s="51">
+        <v>67589</v>
       </c>
       <c r="M75" s="8">
         <v>52793</v>
@@ -6412,7 +6421,7 @@
       <c r="Y75" s="8"/>
       <c r="AA75" s="37">
         <f>SUM(K75:Y75)</f>
-        <v>757180</v>
+        <v>743862</v>
       </c>
       <c r="AB75" s="37">
         <f>SUM(K76:Y76)</f>
@@ -6424,7 +6433,7 @@
       </c>
       <c r="AE75" s="37">
         <f t="shared" si="1"/>
-        <v>13318</v>
+        <v>0</v>
       </c>
       <c r="AF75" s="37">
         <f t="shared" si="1"/>
@@ -6977,7 +6986,7 @@
       <c r="Y84" s="14"/>
       <c r="AA84" s="43">
         <f>SUM(AA75:AA83)</f>
-        <v>2507894</v>
+        <v>2494576</v>
       </c>
       <c r="AB84" s="43">
         <f>SUM(AB75:AB83)</f>
@@ -6989,7 +6998,7 @@
       </c>
       <c r="AE84" s="43">
         <f t="shared" ref="AE84:AG85" si="2">AA84-B84</f>
-        <v>13327</v>
+        <v>9</v>
       </c>
       <c r="AF84" s="43">
         <f t="shared" si="2"/>
@@ -9010,8 +9019,8 @@
       <c r="R112" s="8">
         <v>206811</v>
       </c>
-      <c r="S112" s="8">
-        <v>173633</v>
+      <c r="S112" s="51">
+        <v>183627</v>
       </c>
       <c r="T112" s="8">
         <v>161997</v>
@@ -9033,7 +9042,7 @@
       </c>
       <c r="AA112" s="37">
         <f>SUM(K112:Y112)</f>
-        <v>2636749</v>
+        <v>2646743</v>
       </c>
       <c r="AB112" s="37">
         <f>SUM(K113:Y113)</f>
@@ -9045,7 +9054,7 @@
       </c>
       <c r="AE112" s="37">
         <f>AA112-B112</f>
-        <v>-9994</v>
+        <v>0</v>
       </c>
       <c r="AF112" s="37">
         <f>AB112-C112</f>
@@ -9278,7 +9287,7 @@
       </c>
       <c r="AC115" s="37">
         <f>SUM(K117:Y117)</f>
-        <v>66703</v>
+        <v>64703</v>
       </c>
       <c r="AE115" s="37">
         <f>AA115-B115</f>
@@ -9290,7 +9299,7 @@
       </c>
       <c r="AG115" s="37">
         <f>AC115-D115</f>
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AI115" s="38">
         <f>C115/B115*1000</f>
@@ -9406,8 +9415,8 @@
       <c r="Q117" s="5">
         <v>4240</v>
       </c>
-      <c r="R117" s="5">
-        <v>6824</v>
+      <c r="R117" s="51">
+        <v>4824</v>
       </c>
       <c r="S117" s="5">
         <v>5024</v>
@@ -9547,8 +9556,8 @@
       <c r="Q119" s="8">
         <v>120384</v>
       </c>
-      <c r="R119" s="8">
-        <v>147611</v>
+      <c r="R119" s="51">
+        <v>207611</v>
       </c>
       <c r="S119" s="8">
         <v>111605</v>
@@ -9556,8 +9565,8 @@
       <c r="T119" s="8">
         <v>112222</v>
       </c>
-      <c r="U119" s="8">
-        <v>128352</v>
+      <c r="U119" s="51">
+        <v>178352</v>
       </c>
       <c r="V119" s="8"/>
       <c r="W119" s="8"/>
@@ -9565,7 +9574,7 @@
       <c r="Y119" s="8"/>
       <c r="AA119" s="37">
         <f>SUM(K119:Y119)</f>
-        <v>1537571</v>
+        <v>1647571</v>
       </c>
       <c r="AB119" s="37">
         <f>SUM(K120:Y120)</f>
@@ -9577,7 +9586,7 @@
       </c>
       <c r="AE119" s="37">
         <f>AA119-B119</f>
-        <v>-110000</v>
+        <v>0</v>
       </c>
       <c r="AF119" s="37">
         <f>AB119-C119</f>
@@ -10846,8 +10855,8 @@
       <c r="V137" s="8">
         <v>184123</v>
       </c>
-      <c r="W137" s="8">
-        <v>213455</v>
+      <c r="W137" s="51">
+        <v>231455</v>
       </c>
       <c r="X137" s="8">
         <v>224772</v>
@@ -10857,7 +10866,7 @@
       </c>
       <c r="AA137" s="37">
         <f>SUM(K137:Y137)</f>
-        <v>3126051</v>
+        <v>3144051</v>
       </c>
       <c r="AB137" s="37">
         <f>SUM(K138:Y138)</f>
@@ -10869,7 +10878,7 @@
       </c>
       <c r="AE137" s="37">
         <f>AA137-B137</f>
-        <v>-18000</v>
+        <v>0</v>
       </c>
       <c r="AF137" s="37">
         <f>AB137-C137</f>
@@ -11479,8 +11488,8 @@
       <c r="L146" s="8">
         <v>303234</v>
       </c>
-      <c r="M146" s="8">
-        <v>586235</v>
+      <c r="M146" s="51">
+        <v>406235</v>
       </c>
       <c r="N146" s="8">
         <v>473512</v>
@@ -11504,7 +11513,7 @@
       <c r="Y146" s="8"/>
       <c r="AA146" s="37">
         <f>SUM(K146:Y146)</f>
-        <v>2919528</v>
+        <v>2739528</v>
       </c>
       <c r="AB146" s="37">
         <f>SUM(K147:Y147)</f>
@@ -11516,7 +11525,7 @@
       </c>
       <c r="AE146" s="37">
         <f>AA146-B146</f>
-        <v>180000</v>
+        <v>0</v>
       </c>
       <c r="AF146" s="37">
         <f>AB146-C146</f>
@@ -12803,8 +12812,8 @@
       <c r="T165" s="8">
         <v>164985</v>
       </c>
-      <c r="U165" s="8">
-        <v>217697</v>
+      <c r="U165" s="51">
+        <v>226697</v>
       </c>
       <c r="V165" s="8">
         <v>181294</v>
@@ -12814,7 +12823,7 @@
       <c r="Y165" s="8"/>
       <c r="AA165" s="37">
         <f>SUM(K165:Y165)</f>
-        <v>2978710</v>
+        <v>2987710</v>
       </c>
       <c r="AB165" s="37">
         <f>SUM(K166:Y166)</f>
@@ -12826,7 +12835,7 @@
       </c>
       <c r="AE165" s="37">
         <f>AA165-B165</f>
-        <v>-9000</v>
+        <v>0</v>
       </c>
       <c r="AF165" s="37">
         <f>AB165-C165</f>
@@ -13672,7 +13681,7 @@
       </c>
       <c r="AB177" s="37">
         <f>SUM(K178:Y178)</f>
-        <v>134444</v>
+        <v>135444</v>
       </c>
       <c r="AC177" s="37">
         <f>SUM(K179:Y179)</f>
@@ -13684,7 +13693,7 @@
       </c>
       <c r="AF177" s="37">
         <f>AB177-C177</f>
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="AG177" s="37">
         <f>AC177-D177</f>
@@ -13727,8 +13736,8 @@
       <c r="K178" s="5">
         <v>16088</v>
       </c>
-      <c r="L178" s="5">
-        <v>7221</v>
+      <c r="L178" s="51">
+        <v>8221</v>
       </c>
       <c r="M178" s="5">
         <v>8019</v>
@@ -13821,8 +13830,8 @@
       <c r="A180" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="B180" s="18">
-        <v>2029441</v>
+      <c r="B180" s="51">
+        <v>2038325</v>
       </c>
       <c r="C180" s="18">
         <v>109047</v>
@@ -13887,7 +13896,7 @@
       </c>
       <c r="AE180" s="37">
         <f>AA180-B180</f>
-        <v>8884</v>
+        <v>0</v>
       </c>
       <c r="AF180" s="37">
         <f>AB180-C180</f>
@@ -13899,19 +13908,19 @@
       </c>
       <c r="AI180" s="38">
         <f>C180/B180*1000</f>
-        <v>53.732530287897013</v>
+        <v>53.498338096230974</v>
       </c>
       <c r="AJ180" s="38">
         <f>D180/B180*1000</f>
-        <v>30.209796687856411</v>
+        <v>30.07812787460292</v>
       </c>
       <c r="AL180" s="38">
         <f>AI180-H180</f>
-        <v>3.2530287897010624E-2</v>
+        <v>-0.20166190376902904</v>
       </c>
       <c r="AM180" s="38">
         <f>AJ180-I180</f>
-        <v>9.7966878564115234E-3</v>
+        <v>-0.12187212539707915</v>
       </c>
     </row>
     <row r="181" spans="1:39">
@@ -14630,27 +14639,27 @@
       <c r="Y191" s="22"/>
       <c r="AA191" s="43">
         <f>SUM(AA85:AA190)</f>
-        <v>68336489</v>
+        <v>68303483</v>
       </c>
       <c r="AB191" s="43">
         <f>SUM(AB85:AB190)</f>
-        <v>3329702</v>
+        <v>3330702</v>
       </c>
       <c r="AC191" s="43">
         <f>SUM(AC85:AC190)</f>
-        <v>2426048</v>
+        <v>2424048</v>
       </c>
       <c r="AE191" s="43">
         <f t="shared" ref="AE191:AG192" si="4">AA191-B191</f>
-        <v>128845</v>
+        <v>95839</v>
       </c>
       <c r="AF191" s="43">
         <f t="shared" si="4"/>
-        <v>-11747</v>
+        <v>-10747</v>
       </c>
       <c r="AG191" s="43">
         <f t="shared" si="4"/>
-        <v>40131</v>
+        <v>38131</v>
       </c>
       <c r="AI191" s="44">
         <f>C191/B191*1000</f>
@@ -14914,27 +14923,27 @@
       <c r="Y195" s="22"/>
       <c r="AA195" s="45">
         <f>SUM(AA42, AA84, AA74, AA191, AA192)</f>
-        <v>104577725</v>
+        <v>104531401</v>
       </c>
       <c r="AB195" s="45">
         <f>SUM(AB42, AB84, AB74, AB191, AB192)</f>
-        <v>4918532</v>
+        <v>4919532</v>
       </c>
       <c r="AC195" s="45">
         <f>SUM(AC42, AC84, AC74, AC191, AC192)</f>
-        <v>3435421</v>
+        <v>3433421</v>
       </c>
       <c r="AE195" s="43">
         <f t="shared" ref="AE195:AG196" si="5">AA195-B195</f>
-        <v>70845</v>
+        <v>24521</v>
       </c>
       <c r="AF195" s="43">
         <f t="shared" si="5"/>
-        <v>722273</v>
+        <v>723273</v>
       </c>
       <c r="AG195" s="43">
         <f t="shared" si="5"/>
-        <v>49936</v>
+        <v>47936</v>
       </c>
       <c r="AI195" s="44">
         <f>C195/B195*1000</f>
@@ -19260,7 +19269,7 @@
       </c>
       <c r="AC263" s="37">
         <f>SUM(K265:Y265)</f>
-        <v>8295</v>
+        <v>7295</v>
       </c>
       <c r="AE263" s="37">
         <f>AA263-B263</f>
@@ -19272,7 +19281,7 @@
       </c>
       <c r="AG263" s="37">
         <f>AC263-D263</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI263" s="38">
         <f>C263/B263*1000</f>
@@ -19351,8 +19360,8 @@
       <c r="L265" s="5">
         <v>1043</v>
       </c>
-      <c r="M265" s="5">
-        <v>1855</v>
+      <c r="M265" s="51">
+        <v>855</v>
       </c>
       <c r="N265" s="5">
         <v>1291</v>
@@ -19743,8 +19752,8 @@
       <c r="A272" s="32" t="s">
         <v>272</v>
       </c>
-      <c r="B272" s="33">
-        <v>375383</v>
+      <c r="B272" s="51">
+        <v>373385</v>
       </c>
       <c r="C272" s="33">
         <v>10092</v>
@@ -19805,7 +19814,7 @@
       </c>
       <c r="AE272" s="37">
         <f>AA272-B272</f>
-        <v>-1998</v>
+        <v>0</v>
       </c>
       <c r="AF272" s="37">
         <f>AB272-C272</f>
@@ -19817,11 +19826,11 @@
       </c>
       <c r="AI272" s="38">
         <f>C272/B272*1000</f>
-        <v>26.8845419211845</v>
+        <v>27.028402319321877</v>
       </c>
       <c r="AJ272" s="38">
         <f>D272/B272*1000</f>
-        <v>16.561751597701548</v>
+        <v>16.650374278559664</v>
       </c>
       <c r="AL272" s="38"/>
       <c r="AM272" s="38"/>
@@ -19937,8 +19946,8 @@
         <v>9</v>
       </c>
       <c r="J275" s="5"/>
-      <c r="K275" s="33">
-        <v>236586</v>
+      <c r="K275" s="51">
+        <v>226586</v>
       </c>
       <c r="L275" s="33">
         <v>100338</v>
@@ -19962,7 +19971,7 @@
       <c r="Y275" s="33"/>
       <c r="AA275" s="37">
         <f>SUM(K275:Y275)</f>
-        <v>568220</v>
+        <v>558220</v>
       </c>
       <c r="AB275" s="37">
         <f>SUM(K276:Y276)</f>
@@ -19974,7 +19983,7 @@
       </c>
       <c r="AE275" s="37">
         <f>AA275-B275</f>
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AF275" s="37">
         <f>AB275-C275</f>
@@ -20298,7 +20307,7 @@
       <c r="Y281" s="41"/>
       <c r="AA281" s="43">
         <f>SUM(AA254:AA280)</f>
-        <v>5900818</v>
+        <v>5890818</v>
       </c>
       <c r="AB281" s="43">
         <f>SUM(AB254:AB280)</f>
@@ -20306,11 +20315,11 @@
       </c>
       <c r="AC281" s="43">
         <f>SUM(AC254:AC280)</f>
-        <v>85855</v>
+        <v>84855</v>
       </c>
       <c r="AE281" s="43">
         <f t="shared" ref="AE281:AG282" si="8">AA281-B281</f>
-        <v>-674683</v>
+        <v>-684683</v>
       </c>
       <c r="AF281" s="43">
         <f t="shared" si="8"/>
@@ -20318,7 +20327,7 @@
       </c>
       <c r="AG281" s="43">
         <f t="shared" si="8"/>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI281" s="44">
         <f>C281/B281*1000</f>
@@ -20377,27 +20386,27 @@
       <c r="Y282" s="41"/>
       <c r="AA282" s="45">
         <f>SUM(AA195, AA227, AA253, AA281)</f>
-        <v>123625802</v>
+        <v>123569478</v>
       </c>
       <c r="AB282" s="45">
         <f>SUM(AB195, AB227, AB253, AB281)</f>
-        <v>5635258</v>
+        <v>5636258</v>
       </c>
       <c r="AC282" s="45">
         <f>SUM(AC195, AC227, AC253, AC281)</f>
-        <v>3910126</v>
+        <v>3907126</v>
       </c>
       <c r="AE282" s="43">
         <f t="shared" si="8"/>
-        <v>-1172896</v>
+        <v>-1229220</v>
       </c>
       <c r="AF282" s="43">
         <f t="shared" si="8"/>
-        <v>-15805</v>
+        <v>-14805</v>
       </c>
       <c r="AG282" s="43">
         <f t="shared" si="8"/>
-        <v>40190</v>
+        <v>37190</v>
       </c>
       <c r="AI282" s="44">
         <f>C282/B282*1000</f>
